--- a/mistral-small-latest.xlsx
+++ b/mistral-small-latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG19"/>
+  <dimension ref="A1:AG44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3548,6 +3548,4131 @@
         </is>
       </c>
       <c r="AG19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2024-1-EderSands-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>mistral-small-latest</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1915</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Ondar Fishing Company Limited</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1 fatality</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>North Atlantic</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Wind westerly at 8kts; 1m seas; dark, with good visibility; estimated sea temperature 14.8°C</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Shooting fishing gear</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>good visibility</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2024-1-EderSands-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>mistral-small-latest</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1915</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Ondar Fishing Company Limited</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1 fatality</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>North Atlantic</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Wind westerly at 8kts; 1m seas; dark, with good visibility; estimated sea temperature 14.8°C.</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>shooting fishing gear</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>good visibility</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2023-2-HarrietJ-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>mistral-small-latest</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>28 August 2021 at about 0736</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Privately owned</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>- (The vessel was not heading to a specific destination, it was fishing)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>5.4 knots</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1 fatality</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>North Sea</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Long 1.2m northerly swell; air temperature 12°C; wind south-westerly force 3; sea temperature approximately 15°C</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>The skipper of Harriet J  worked three fleets of creels in the bay near to Siccar Point, hauling each fleet while heading broadly west at approximately 1 knot, before reversing direction at roughly 5 knots over the ground to shoot the fleet in the same position.</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>0736</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>less than 5m</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>Yes, 100% decrease in speed from 5.4 knots to 0 knots.</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>3 hours</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Yes, 0.9 nautical miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2023-2-HarrietJ-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>mistral-small-latest</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>28 August 2021 at about 0736</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Privately owned</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>- (The vessel was not heading to a specific destination but was engaged in fishing operations.)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>5.4kts</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1 fatality</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>North Sea</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Long 1.2m northerly swell; air temperature 12°C; wind south-westerly force 3; sea temperature approximately 15°C</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>The skipper of Harriet J  worked three fleets of creels in the bay near to Siccar Point, hauling each fleet while heading broadly west at approximately 1 knot (kt), before reversing direction at roughly 5 knots (kts) over the ground to shoot the fleet in the same position. At about 0700, having brought Harriet J  closer inshore to a position 0.5 nautical miles (nm) north of Meikle Poo Craig, the skipper started to slowly motor the boat on a westerly course along the coast while hauling the fourth fleet of creels. At about 0730, Harriet J  circled round to the south, picking up speed, and settled on a heading of 095° at 5.4kts. At 0736, the track of Harriet J  showed a notable dip in speed while shooting the fourth fleet</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>0736</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>less than 5m</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>Yes, 100% decrease in speed from 5.4kts to 0kts.</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>3 hours</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>0.9nm</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2023-2-HarrietJ-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>mistral-small-latest</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>28 August 2021 at about 0736</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Privately owned</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>- (The vessel was heading west along the coast towards Siccar Point, but it is not explicitly stated where it was ultimately heading.)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>5.4kts</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>1 fatality</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>North Sea</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Long 1.2m northerly swell; air temperature 12°C; wind south-westerly force 3; sea temperature approximately 15°C</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>The skipper of Harriet J  worked three fleets of creels in the bay near to Siccar Point, hauling each fleet while heading broadly west at approximately 1 knot (kt), before reversing direction at roughly 5 knots (kts) over the ground to shoot the fleet in the same position. At about 0730, Harriet J  circled round to the south, picking up speed, and settled on a heading of 095° at 5.4kts. At 0736, the track of Harriet J  showed a notable dip in speed while shooting the fourth fleet of creels.</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>0736</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>less than 5m</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>Yes, 100% (from 5.4kts to 0kts)</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>3 hours</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Yes, 0.9 nautical miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2023-1-EmmaLouise-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>mistral-small-latest</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>11 January 2022 in the early evening</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>William Traynor</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2 fatalities</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>The boat’s engine was running while they remained in the boat’s covered cockpit area.</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Light northerly wind; drizzle; 10°C.</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>The owner called his wife and told her that he and his brother-in-law were on board Emma Louise.</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>The owner and his brother-in-law each drank a beer.</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>**in the early evening**</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>**2**</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>**-**</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>**-**</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>**-**</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>160kg</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2023-1-EmmaLouise-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>mistral-small-latest</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>11 January 2022 in the early evening</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>William Traynor</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2 fatalities</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>The boat’s engine was running while they remained in the boat’s covered cockpit area</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Light northerly wind; drizzle; 10°C.</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>The owner called his wife and told her that he and his brother-in-law were on board Emma Louise.</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>The owner and his brother-in-law each drank a beer.</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>**in the early evening**</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>**2**</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>**-**</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>**-**</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>**-**</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2022-14-ReulAChuain.pdf</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>mistral-small-latest</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1959</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1 fatality</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Sound of Rùm</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>a force 6, creating a short steep swell that caused Reul A Chuain to roll heavily</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>The senior deckhand was standing on the net, attempting to bring it back on board</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Mallaig ALB</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>foredeck</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>The crew had completed the four mandatory SeaFish Industry Authority (Seafish) safety courses. The skipper and senior deckhand had also completed a safety awareness and risk assessment course.</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>1850 (GMT+1)</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>3 (three crew)</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>1 hour 5 minutes</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>Yes, 50%</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2022-14-ReulAChuain.pdf</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>mistral-small-latest</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1959</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1 fatality</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Sound of Rùm</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>The wind had veered to the north and increased to a force 6, creating a short steep swell that caused Reul A Chuain to roll heavily.</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>The senior deckhand went aft to assist, climbed on top of the net on the deck, and helped pull it in.</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Mallaig ALB</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>foredeck</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>The crew had completed the four mandatory SeaFish Industry Authority (Seafish) safety courses. The skipper and senior deckhand had also completed a safety awareness and risk assessment course, which was required for crew with 2 years’ experience or more. Neither of the deckhands had completed practical man overboard drills during their time on board.</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>1850</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>1 hour 15 minutes</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>Yes, 50% (from 6.5kts to 3kts)</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2022-11-Goodway-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>mistral-small-latest</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>16 October 2021 at about 1340</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Joe Masson</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Cairnbulg Briggs reef, north-east of Cairnbulg Point</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>One presumed fatality</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>North Sea</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Wind force 2 to 3, slight sea, low swell, sea temperature 12°C, visibility good.</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>The owner was fishing alone, near to where his vessel was found, and that it was anchored to a fleet of creels on the seabed.</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>visibility good</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2022-11-Goodway-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>mistral-small-latest</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Joe Masson</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Cairnbulg Briggs reef</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>One presumed fatality</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>North Sea</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Wind force 2 to 3, slight sea, low swell, sea temperature 12°C, visibility good</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>The owner was using a burst of engine power to free the creels</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>visibility good</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2022-10-Bella-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>mistral-small-latest</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>At about 1506 on 6 July 2021</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Geosight Limited</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>North-west</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>About 5 knots</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>"Mayday!"</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Wind force 3, waves up to 1m</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>The crew member went forward and lowered the multibeam echo sounder (MBES) gantry from its stowed position into the sea.</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>rigid inflatable boats (RIB)</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Yes, "the crew member used a mobile phone to report the emergency to the supervisor ashore and then, at 1506, called 999 to notify the coastguard."</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>No, "Bella was Geosight’s first commercial survey vessel and the company had operated it for 18 months without incident."</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Not applicable, "Cargo information None"</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Partially, "The crew member did not hold a valid seafarers’ medical certificate and had not completed any other marine training."</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>1506</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2, the skipper and a crew member</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2022-10-Bella-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>mistral-small-latest</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1506 on 6 July 2021</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Geosight Limited</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>north-west</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>5 knots</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>"Mayday!"</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>wind north-westerly force 3; wave height 0.5m-1.0m</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>the crew member went forward and lowered the multibeam echo sounder (MBES) gantry from its stowed position into the sea</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>rigid inflatable boats (RIB)</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>"Mayday!" call using the hand-held very high frequency (VHF) radio</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>"In 2005, the MAIB investigated the hull failure of the RIB Big Yellow"</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>"Cargo information None"</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>"The crew member did not hold a valid seafarers’ medical certificate and had not completed any other marine training."</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>1506</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2022-6-SaintPeter-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>mistral-small-latest</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2 May 2021, between 0800 and 1000</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Privately owned</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Cove, Scotland</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>One fatality</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>**North Sea**</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>**shooting creels**</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>'-'</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>'-'</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>'-'</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>'-'</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>'-'</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>0830</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2022-6-SaintPeter-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>mistral-small-latest</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2 May 2021, between 0800 and 1000</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Privately owned</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Cove, Scotland</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>One fatality</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>**North Sea**</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>**shooting creels**</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>'-'</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>'-'</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>'-'</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>'-'</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>'-'</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>0830</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2022-6-SaintPeter-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>mistral-small-latest</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2 May 2021, between 0800 and 1000</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Privately owned</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Cove, Scotland</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>One fatality</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>**North Sea**</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>**shooting creels**</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>'-'</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>'-'</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>'-'</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>'-'</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>'-'</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>0830</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2021-14-Achieve-Talis-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>mistral-small-latest</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>8 November 2020 at 1541</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>WeShips Denizcilik ve Ticaret A.Ş.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Terneuzen, Netherlands</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>8 knots (kts)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>"Achieve ’s skipper was prompt in calling Humber Coastguard to inform them of the collision and his predicament with flooding."</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>"Wind SSE force 2 to 3, slight sea, low swell. Overcast, poor visibility in patchy fog."</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>"The skipper left the wheelhouse and went to the aft shelter deck to check on the deckhand’s progress."</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>"Tynemouth RNLI all-weather lifeboat (ALB)"</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>"At 1544, Achieve ’s skipper called Humber Coastguard on very high frequency (VHF) radio channel 16"</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>"Both the skipper and the deckhand had completed all UK statutory safety courses"</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>1538</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2 (skipper and deckhand)</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>1 hour 17 minutes</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>1nm</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>'-'</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>'-'</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>'-'</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>2646 tons</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>'-'</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2021-14-Achieve-Talis-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>mistral-small-latest</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>-.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1992.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>-.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>-.</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Yes, "Achieve ’s skipper was prompt in calling Humber Coastguard to inform them of the collision and his predicament with flooding."</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>"Wind SSE force 2 to 3, slight sea, low swell. Overcast, poor visibility in patchy fog."</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>"The skipper left the wheelhouse and went to the aft shelter deck to check on the deckhand’s progress."</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>"Tynemouth RNLI all-weather lifeboat (ALB)"</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>"At 1544, Achieve ’s skipper called Humber Coastguard on very high frequency (VHF) radio channel 16 and advised them he had been in a collision and was taking on water."</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>"Both the skipper and the deckhand had completed all UK statutory safety courses."</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>1538</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2 (skipper and deckhand)</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>16 minutes</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>1 nautical mile</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>The visibility was restricted with fog patches.</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>2646 tons</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2021-14-Achieve-Talis-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>mistral-small-latest</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>**6 November 1997**</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>**-**</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>**-**</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>**-**</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>**-**</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>**8 November 2020**</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>**-**</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>**no**</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>**no**</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>**yes**</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>"Wind SSE force 2 to 3, slight sea, low swell. Overcast, poor visibility in patchy fog."</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>"The skipper left the wheelhouse and went to the aft shelter deck to check on the deckhand’s progress."</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>"Tynemouth RNLI all-weather lifeboat (ALB)"</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>"At 1544, Achieve ’s skipper called Humber Coastguard on very high frequency (VHF) radio channel 16 and advised them he had been in a collision and was taking on water."</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>"Both the skipper and the deckhand had completed all UK statutory safety courses."</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>1538</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2 (a skipper and a deckhand)</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>16 minutes</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>1nm</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>'-'</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>'-'</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>'-'</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>2646 tons</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>'-'</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2021-10-Globetrotter-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mistral-small-latest</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>One fatality</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>"steering problems"</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>"bilge pumps"</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>"Mayday"</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Irish Sea</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>The weather was fine and clear, the wind was easterly Beaufort force 3 to 4, the tide was ebbing in a south-westerly direction at a rate of about 0.6 knot, and the sea water temperature was 15.3°C.</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>The owner’s son pointed out to his father that there was water on the deck aft. Globetrotter ’s owner looked aft and saw that the water level was about 10cm above the deck and rising.</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Fleetwood Royal National Lifeboat Institution (RNLI) inshore lifeboat and Fleetwood’s all-weather lifeboat</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>"the cabin space" and "by the cabin door"</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>"At 0742, Globetrotter ’s owner used the hand-held radio to broadcast a “Mayday” on VHF channel 16."</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>"Globetrotter had completed a trip to sea in September 2019"</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>"-"</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>"Globetrotter ’s owner held a VHF Radio Licence but had no yachting or boating qualifications and had not completed any maritime courses. He had no knowledge of the regulations or guidance that were applicable to him as a non-professional mariner."</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>Three people: Globetrotter’s owner, his son, and his friend</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>19 minutes</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2021-10-Globetrotter-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>mistral-small-latest</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>One fatality</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>"steering problems"</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>"bilge pumps"</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>"Mayday"</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Irish Sea</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>The weather was fine and clear, the wind was easterly Beaufort force 3 to 4, the tide was ebbing in a south-westerly direction at a rate of about 0.6 knot, and the sea water temperature was 15.3°C.</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>The owner’s son pointed out to his father that there was water on the deck aft. Globetrotter ’s owner looked aft and saw that the water level was about 10cm above the deck and rising. The owner quickly realised that the boat was flooding rapidly and passed the helm to his friend. He then ran to the deck and looked over the stern to check the bilge pumps’ discharge, but the outlets were already submerged. The owner began to bail the water out using a bucket, while his friend placed the engine control to neutral, left the wheelhouse and went onto the deck.</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Fleetwood Royal National Lifeboat Institution (RNLI) inshore lifeboat, Fleetwood’s all-weather lifeboat</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>"the cabin space" and "by the cabin door"</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>"At 0742, Globetrotter ’s owner used the hand-held radio to broadcast a “Mayday” on VHF channel 16."</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>"-"</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>"-"</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>"Globetrotter ’s owner was at the helm and his son and friend were on the outer deck; neither was wearing a personal flotation device (PFD)."</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>3 people: Globetrotter’s owner, his son, and his friend</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>19 minutes</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2021-06-BeinnNaCaillich.pdf</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>mistral-small-latest</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Marine Harvest (Scotland) Limited</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ardintoul fish farm site</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>The two workboat deckhands, unaware that the transfer was about to take place, remained in the galley.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1 fatality</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>The hand side of the ladder was missing after becoming detached following a heavy contact during a feed delivery on 8 February 2020.</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>At 1520, Stornoway Coastguard received a “Mayday” call from the barge on very high frequency (VHF) radio channel 16, and shortly afterwards a “Mayday” call from Beinn Na Caillich.</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>"the wind was south-westerly at 15 knots, the sea state was slight, the air temperature was 5°C and the water temperature was about 7°C."</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>"the assistant manager was attempting to climb on to the barge from the workboat Beinn Na Caillich and fell into the water after being crushed between the boat and the barge."</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>"rigid buoyancy boats (RBB)"</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>"Mayday" call</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>"The crew had not conducted manoverboard drills and it was evident that they were unfamiliar with the workboat’s manoverboard recovery equipment."</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2021-06-BeinnNaCaillich.pdf</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>mistral-small-latest</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Marine Harvest (Scotland) Limited</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ardintoul fish farm site</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>The two workboat deckhands, unaware that the transfer was about to take place, remained in the galley.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1 fatality</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>The hand side of the ladder was missing after becoming detached following a heavy contact during a feed delivery on 8 February 2020.</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>At 1520, Stornoway Coastguard received a “Mayday” call from the barge on very high frequency (VHF) radio channel 16, and shortly afterwards a “Mayday” call from Beinn Na Caillich.</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>"the wind was south-westerly at 15 knots, the sea state was slight, the air temperature was 5°C and the water temperature was about 7°C."</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>"the assistant manager was attempting to climb on to the barge from the workboat Beinn Na Caillich and fell into the water after being crushed between the boat and the barge."</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>"rigid buoyancy boats (RBB)"</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>"Mayday" call</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>"The crew had not conducted manoverboard drills and it was evident that they were unfamiliar with the workboat’s manoverboard recovery equipment."</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2021-Seadogz_InterimReport.pdf</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>mistral-small-latest</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1011:09</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Seadogz Rib Charter Ltd</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>38.4kts</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Yes, 1 fatality</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Yes, the execution of the Seadogz Experience Ride conducted on 22 August 2020 was not untypical of such operations.</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Southampton Water</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>overcast with bright spells, the winds were 17kts from the west-south-west with gusts of 25kts, and the sea state was slight</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>conducting high speed manoeuvres in close proximity to another vessel</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>"The skipper was a highly qualified and experienced RIB driver"</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>10:11:09</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>good visibility</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>0.45 hours</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2021-Seadogz_InterimReport.pdf</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>mistral-small-latest</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1011:09</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Seadogz Rib Charter Ltd</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>38.4kts</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Yes, 1 fatality</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Southampton Water</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>West-south-westerly winds, force 4-5, slight seas, overcast with bright spells, good visibility</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>The skipper was operating single-handedly, at high speed and did not see the navigation buoy, which was directly ahead, for 10 seconds before impact.</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>"The skipper was a highly qualified and experienced RIB driver"</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>10:11:09</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>good visibility</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>0.45 hours</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
